--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>321.2</v>
+        <v>292.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>27.9</v>
@@ -748,39 +748,33 @@
         <v>18.5</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>81.7</v>
+        <v>89.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1564.4</v>
+        <v>152444.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.9</v>
+        <v>42.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N4" s="8" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n">
         <v>1.4</v>
       </c>
@@ -788,19 +782,19 @@
         <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>28.9</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>71</v>
+        <v>712.9</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>7.8</v>
@@ -822,7 +816,7 @@
         <v>382.4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>26.9</v>
+        <v>21.9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>11.5</v>
@@ -830,17 +824,17 @@
       <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>15.4</v>
+      <c r="G5" s="8" t="n">
+        <v>25.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
@@ -848,45 +842,43 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n">
-        <v>2.4</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>8.6</v>
+        <v>840.5</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.9</v>
+        <v>26.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>80.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -902,7 +894,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>309.1</v>
+        <v>39.1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>25.9</v>
@@ -911,10 +903,10 @@
         <v>10.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -923,52 +915,52 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.1</v>
+        <v>12.1</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4</v>
+        <v>41.4</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>13.1</v>
+      <c r="N6" s="8" t="n">
+        <v>37.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10.2</v>
+      <c r="P6" s="8" t="n">
+        <v>60.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>15.8</v>
+        <v>5.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>15.3</v>
+        <v>454.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.9</v>
@@ -993,7 +985,7 @@
         <v>21.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>17.9</v>
@@ -1002,32 +994,32 @@
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>444.9</v>
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>13.2</v>
+      <c r="L7" s="3" t="n">
+        <v>3.2</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>34.1</v>
+        <v>3.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>19.3</v>
+        <v>114.3</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>16.8</v>
@@ -1036,10 +1028,10 @@
         <v>3.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>919</v>
+        <v>73990.89999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>49.8</v>
+        <v>4.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
@@ -1054,7 +1046,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1079,46 +1071,46 @@
         <v>10.5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.5</v>
+        <v>38.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>29.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>76</v>
@@ -1130,9 +1122,9 @@
         <v>18.7</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1155,68 +1147,64 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>149.7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>289.5</v>
+        <v>1289.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>55</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>213.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.3</v>
+        <v>73.2</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>13.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>7.7</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n">
-        <v>56.7</v>
+        <v>5.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>554.2</v>
+        <v>531.1</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>48421.2</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>484912.4</v>
+      </c>
+      <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>935.9</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>414.5</v>
@@ -1241,30 +1229,33 @@
         <v>349.9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+4244 3
+</t>
+        </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148 1
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+        <v>18.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n">
-        <v>11.3</v>
+        <v>551.2</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>11</v>
@@ -1279,28 +1270,26 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>26.7</v>
+      </c>
+      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
+        <v>29.9</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>18.2</v>
+        <v>431.2</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
@@ -1320,7 +1309,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>27.3</v>
@@ -1328,64 +1317,79 @@
       <c r="E11" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>13</v>
+      <c r="F11" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+        <v>16.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="I11" s="3" t="n">
-        <v>4.9</v>
+        <v>20.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
+        <v>6.9</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24242
+22
+144561919
+</t>
+        </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>23</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>266.3</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>17.1</v>
+        <v>12.1</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>427.7</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>19.9</v>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+741
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>9.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X11" s="8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>660.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1401,41 +1405,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>10.9</v>
+        <v>251.1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>93.90000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>5.8</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>15.9</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>41.1</v>
-      </c>
+      <c r="L12" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
@@ -1444,30 +1444,24 @@
         <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>14.7</v>
+        <v>43.5</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="Z12" s="3" t="n">
-        <v>2.2</v>
-      </c>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1485,71 +1479,73 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>253.5</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>81.3</v>
+        <v>1.2</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>444.1</v>
+        <v>14.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.4</v>
+        <v>4.9</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>191.6</v>
+        <v>11.2</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>44.1</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>4.6</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>197</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="3" t="n"/>
+      <c r="V13" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W13" s="3" t="n">
-        <v>17.7</v>
+        <v>27.7</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1565,40 +1561,38 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>181.3</v>
+      <c r="E14" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
+        <v>82.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.3</v>
+        <v>15.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>13</v>
+        <v>11.8</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>44.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1610,27 +1604,29 @@
       <c r="R14" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>56.6</v>
+      <c r="S14" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="W14" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1646,76 +1642,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>229</v>
+        <v>639</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>81.5</v>
+      <c r="E15" s="8" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.1</v>
+        <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>7.8</v>
+        <v>13.2</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>11.3</v>
+        <v>30.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>434.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>51.7</v>
+        <v>22.6</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>310.8</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1730,73 +1724,73 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>9994.1</v>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+7656
+</t>
+        </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>56.8</v>
+        <v>466.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>92.5</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>39.5</v>
+        <v>3.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>3.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n">
-        <v>59.9</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n">
-        <v>58.2</v>
+        <v>12.3</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>1191.8</v>
+        <v>66.2</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.3</v>
+        <v>7.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>60.9</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n">
-        <v>98.2</v>
+        <v>385.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.1</v>
+        <v>89.2</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>364</v>
+        <v>369.9</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1812,10 +1806,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>445.9</v>
+        <v>2224.9</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>11.4</v>
@@ -1826,57 +1820,67 @@
       <c r="G17" s="3" t="n">
         <v>44.4</v>
       </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>44.8</v>
+      <c r="H17" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>11.8</v>
+        <v>59.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>11.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>41.6</v>
+        <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>971.8</v>
+        <v>4839</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>151.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+1
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+2
+</t>
+        </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>46.2</v>
+        <v>7.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>84.7</v>
+        <v>6.3</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>39.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>1.8</v>
@@ -1895,72 +1899,87 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D18" s="3" t="n"/>
+        <v>45.9</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>25.9</v>
+      </c>
       <c r="E18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>181.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>894.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>7.5</v>
+        <v>15</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+7648
+</t>
+        </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>29.4</v>
+        <v>23.2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>56.5</v>
+        <v>11.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
+        <v>97.8</v>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
+      <c r="R18" s="8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>17.9</v>
+        <v>456.2</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+224
+</t>
+        </is>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>22</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22254
+224
+1111
+</t>
+        </is>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>59</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1976,52 +1995,50 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.1</v>
+        <v>455.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>25.9</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40.9</v>
+        <v>16.6</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>17.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.2</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>1132</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
+        <v>25.4</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>64.2</v>
@@ -2030,19 +2047,19 @@
         <v>48.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.6</v>
+        <v>14.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>6.6</v>
@@ -2061,71 +2078,78 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.1</v>
+        <v>531.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.3</v>
+        <v>19.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>33.5</v>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+2
+72
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>51.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>22.4</v>
+        <v>17.2</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>221.1</v>
+        <v>22.2</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>19.9</v>
+        <v>17.8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>44.4</v>
+        <v>21</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>7.6</v>
@@ -2143,69 +2167,73 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0.7</v>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+3894
+</t>
+        </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.2</v>
+        <v>24.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20.4</v>
+        <v>12.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>121.3</v>
+        <v>18.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.3</v>
+        <v>21.8</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>15.9</v>
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>19.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>393.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>48.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2230,36 +2258,40 @@
         <v>429</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="8" t="n">
-        <v>81.7</v>
+        <v>25.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.3</v>
+        <v>13.7</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>18</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>3.1</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2274,25 +2306,25 @@
         <v>14.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>13.9</v>
+      <c r="W22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>13.4</v>
+        <v>1239.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2308,72 +2340,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
+        <v>232.3</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>25.2</v>
+        <v>13.2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12.1</v>
+        <v>561.1</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>945.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>759.4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>40.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N23" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>99.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n"/>
+      <c r="R23" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>2357.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>88.5</v>
+        <v>4.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>106.7</v>
+        <v>16.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>851.5</v>
+        <v>215.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>86.2</v>
+        <v>13.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>341.5</v>
+        <v>34.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.5</v>
+        <v>60.9</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2389,48 +2425,52 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>464.1</v>
+        <v>46.4</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>32.3</v>
+        <v>26.4</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.1</v>
+        <v>40.5</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>2.4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>42.5</v>
+        <v>62.5</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="N24" s="3" t="n"/>
+        <v>61.8</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>493</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>63.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>17.6</v>
+        <v>88</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
@@ -2438,22 +2478,24 @@
       <c r="T24" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="U24" s="8" t="n">
-        <v>177.4</v>
+      <c r="U24" s="3" t="n">
+        <v>88.5</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>17.2</v>
+        <v>831.5</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+        <v>68.3</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2467,72 +2509,85 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>488.9</v>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4889
+49
+</t>
+        </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>11.3</v>
+        <v>1.4</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.6</v>
+        <v>114.7</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>29.1</v>
+      </c>
+      <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>42.5</v>
+        <v>425.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
+        <v>12.4</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>926</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>1.2</v>
+        <v>17.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.4</v>
+        <v>5.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>469.5</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W25" s="3" t="n"/>
+        <v>49.5</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>772.1</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292575
+111979
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122
+1
+1111919
+</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>66</v>
+        <v>6.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>8.6</v>
@@ -2551,13 +2606,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>340.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1.2</v>
+        <v>9.6</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>17</v>
@@ -2565,30 +2620,30 @@
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>1.6</v>
+      <c r="H26" s="3" t="n">
+        <v>57.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n">
-        <v>10.4</v>
+      <c r="L26" s="8" t="n">
+        <v>10.7</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
@@ -2603,22 +2658,22 @@
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>21.6</v>
+        <v>24.3</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>16.9</v>
+        <v>63.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>12.2</v>
+        <v>1.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2634,52 +2689,50 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>390.2</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>9.6</v>
+        <v>41.4</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>16.2</v>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>14.3</v>
@@ -2688,19 +2741,27 @@
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
+        <v>21.6</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+11737
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78 277
+185
+</t>
+        </is>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2719,25 +2780,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>513.3</v>
+        <v>53.3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>11.1</v>
+        <v>21.5</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>44.3</v>
+        <v>49.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>45.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
@@ -2746,16 +2807,20 @@
         <v>5.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.5</v>
+        <v>124.3</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+1554
+</t>
+        </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
@@ -2773,13 +2838,13 @@
         <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="8" t="n">
-        <v>16.7</v>
+      <c r="W28" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>17</v>
@@ -2804,23 +2869,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>593.3</v>
+        <v>53.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>11.6</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>8.1</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
@@ -2828,48 +2891,52 @@
         <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>790.9</v>
+        <v>1.4</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="N29" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>96</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>472.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>11.2</v>
+        <v>21.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2885,43 +2952,43 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
+        <v>284.8</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>18.8</v>
+        <v>322.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.9</v>
+        <v>522.7</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>91.7</v>
+        <v>67.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>19.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.9</v>
+        <v>5.7</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>32</v>
+        <v>4816.1</v>
       </c>
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="n">
@@ -2931,28 +2998,28 @@
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>34484.5</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>551.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>99.5</v>
+        <v>29.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>17.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2968,32 +3035,32 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>31.2</v>
+        <v>451</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>52.9</v>
+        <v>10.4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10.9</v>
+        <v>19.3</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26</v>
+        <v>12.8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
@@ -3002,22 +3069,22 @@
         <v>0.3</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4516.1</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.6</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>11.1</v>
@@ -3026,16 +3093,16 @@
         <v>19.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>11.1</v>
+        <v>0.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>2.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3051,72 +3118,70 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>43.7</v>
+        <v>520.9</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>26.2</v>
+        <v>22.9</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>10.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>757.4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>41.1</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>59.2</v>
+      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>11.2</v>
+        <v>16.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>24.8</v>
+        <v>26.1</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>42.1</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>116.9</v>
+        <v>22.1</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.5</v>
+        <v>42.1</v>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X32" s="3" t="n"/>
+        <v>12.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y32" s="3" t="n">
         <v>70</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>71.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3132,76 +3197,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>520</v>
+        <v>3497.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>19.9</v>
+        <v>70.2</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17.7</v>
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>29.4</v>
+        <v>3.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n">
-        <v>12.3</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.6</v>
+        <v>98.2</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>20.3</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>62.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>10.3</v>
+        <v>51</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>21.1</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.6</v>
+        <v>3.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>70</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3217,73 +3280,73 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>349.1</v>
+        <v>329.9</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>10.2</v>
+        <v>23.3</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>4.1</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.3</v>
+        <v>4.3</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>16.6</v>
+        <v>16</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.3</v>
+        <v>0.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0.2</v>
+        <v>78.7</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>19.9</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>10.3</v>
+        <v>2.6</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>8582</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3302,77 +3365,75 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>329.9</v>
+        <v>56.7</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.3</v>
+        <v>26.8</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>520.6</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>18.7</v>
-      </c>
       <c r="W35" s="3" t="n">
-        <v>16.8</v>
+        <v>846.3</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>81</v>
+        <v>278.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>68.5</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3387,76 +3448,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>506.7</v>
+        <v>53.5</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>19.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>12.9</v>
+        <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="P36" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="V36" s="3" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>6.2</v>
+        <v>14.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>16.8</v>
+        <v>434.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>68.5</v>
+        <v>9.9</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>212.2</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3472,72 +3533,101 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>535.5</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>26.3</v>
+        <v>24.4</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1188414042
+</t>
+        </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>46</v>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">614242
+149081
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+119019
+</t>
+        </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>14.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>10.6</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>422.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">714531 7
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>10.5</v>
+        <v>92</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753824
+9
+222
+11
+</t>
+        </is>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>25.5</v>
+        <v>111818.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.1</v>
+        <v>8.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>14.8</v>
+        <v>8.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>125</v>
+        <v>3169.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>4.3</v>
+        <v>541.3</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>154.6</v>
+        <v>19.2</v>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">646257
+121191
+</t>
+        </is>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3.3</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>52.8</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>34.6</v>
+        <v>345.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3553,75 +3643,91 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2240.4</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E38" s="8" t="n">
-        <v>10.4</v>
+      <c r="E38" s="3" t="n">
+        <v>6.9</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>99.7</v>
+        <v>94.7</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>46</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>69</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.1</v>
+        <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.8</v>
+        <v>52.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>431.7</v>
+        <v>5.5</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>492</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>151.5</v>
+        <v>74.2</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+727227
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753824
+9
+222
+11
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>115.5</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>216.4</v>
+        <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0.9</v>
+        <v>12.3</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>84.7</v>
+        <v>83.2</v>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+92
+</t>
+        </is>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+        <v>24.9</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>345.6</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3636,73 +3742,82 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4248.1</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>28.5</v>
+        <v>573.9</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>25.7</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>60.9</v>
+        <v>12.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>99.7</v>
+        <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>42.1</v>
+        <v>7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>431.7</v>
+        <v>22.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>151.5</v>
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>10.9</v>
+        <v>78</v>
+      </c>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81556
+15252197
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2227
+191
+</t>
+        </is>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>16.6</v>
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 28
+</t>
+        </is>
       </c>
       <c r="X39" s="3" t="n">
-        <v>84.7</v>
+        <v>12.5</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>741.9</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>5.5</v>
@@ -3721,77 +3836,80 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.7</v>
+        <v>35.7</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+4
+</t>
+        </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>42.2</v>
+        <v>71</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n">
-        <v>12.7</v>
+        <v>0.3</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>5.1</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 0
-</t>
-        </is>
+        <v>40.3</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>993.6</v>
+        <v>26.6</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.1</v>
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>198</v>
+        <v>63.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>212.1</v>
+        <v>13.7</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>88.3</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>76</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3807,76 +3925,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>451.2</v>
+        <v>5.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>11</v>
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>13.1</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>66.5</v>
+      <c r="G41" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>61.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>88.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>57.1</v>
+        <v>8.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>97.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>18.4</v>
+        <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>8</v>
+        <v>51.9</v>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2227
+191
+</t>
+        </is>
       </c>
       <c r="V41" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>16.8</v>
+        <v>22</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.5</v>
+        <v>0.4</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>7.2</v>
+        <v>214.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3892,76 +4014,86 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>451.2</v>
+        <v>5724.4</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>10.7</v>
+        <v>27.2</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>48.9</v>
+        <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>2.2</v>
+      <c r="H42" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>88.5</v>
+        <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>18.8</v>
+        <v>40.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>598</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>55.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">432
+5
+</t>
+        </is>
       </c>
       <c r="U42" s="3" t="n">
-        <v>12.4</v>
+        <v>19.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>89.3</v>
+        <v>161.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>88.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>839</v>
+        <v>58.9</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.4</v>
+        <v>7.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3977,69 +4109,96 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>524.4</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>84.5</v>
+        <v>6666844.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>13.1</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2.3</v>
+        <v>19.3</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>259.7</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
+        <v>51.7</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>12.8</v>
+      </c>
       <c r="I43" s="3" t="n">
-        <v>13.9</v>
+        <v>3.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>43.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717774
+82
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24127
+8
+242257
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1859957
+5
+13 2
+529
+</t>
+        </is>
       </c>
       <c r="O43" s="3" t="n">
-        <v>96</v>
+        <v>0.7</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>23.9</v>
+        <v>2.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>22</v>
+        <v>7.7</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>2222.4</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="X43" s="3" t="n"/>
+        <v>161.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>58.9</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>35.2</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4053,55 +4212,88 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>5724.4</v>
+      </c>
       <c r="D44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>27.2</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+0
+2644
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n">
-        <v>43.4</v>
+        <v>3.9</v>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
+        <v>27.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>23.1</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+21
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.5</v>
+        <v>96</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2424622
+2224
+</t>
+        </is>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="T44" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="U44" s="3" t="n"/>
+        <v>2169.4</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>59.9</v>
+      </c>
       <c r="V44" s="3" t="n">
-        <v>1.1</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4117,7 +4309,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16110.9</v>
+        <v>10197.9</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>109.7</v>
@@ -4132,53 +4324,59 @@
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>56.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>14.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>221.9</v>
+        <v>101.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L45" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>388</v>
+        <v>38</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>66</v>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.4</v>
+        <v>54.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>22222.4</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>21.3</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+      <c r="Y45" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4194,15 +4392,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>477.8</v>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+        <v>47.8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F46" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
@@ -4211,55 +4413,55 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>221.9</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>11.9</v>
+        <v>1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>22.9</v>
+        <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.7</v>
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>71</v>
+        <v>17.7</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>54.9</v>
+        <v>2169.4</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">197 1
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n"/>
+      <c r="W46" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>19.5</v>
       </c>
       <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>292.2</v>
+        <v>391.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>27.9</v>
@@ -748,56 +748,64 @@
         <v>18.5</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>89.7</v>
+        <v>181.7</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" s="8" t="n">
-        <v>152444.7</v>
+      <c r="I4" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>42.9</v>
+        <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P4" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>114.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
+        <v>542.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>2219.1</v>
+      </c>
+      <c r="W4" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>41.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>712.9</v>
+        <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>0.1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -815,70 +823,68 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>21.9</v>
+      <c r="D5" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>11.5</v>
+        <v>44.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19.2</v>
+        <v>41.1</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>25.4</v>
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>17.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" s="3" t="n"/>
+      <c r="L5" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>190.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>26.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>19.5</v>
+        <v>91</v>
+      </c>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="8" t="n">
+        <v>189.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>8.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -894,76 +900,70 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>18.9</v>
+      <c r="F6" s="8" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>12.1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>41.4</v>
+        <v>1.4</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>11</v>
+        <v>411</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>37.1</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>60.2</v>
+        <v>199</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>16.3</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>5.2</v>
+        <v>92</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="8" t="n">
+        <v>715.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>454.3</v>
+        <v>114.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>10.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -979,74 +979,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>275.8</v>
+        <v>1275.8</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.3</v>
+        <v>22.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>9</v>
+        <v>4.1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>11.9</v>
+        <v>444.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>45</v>
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99.2</v>
+        <v>198</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>114.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.1</v>
+        <v>43.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>73990.89999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+        <v>79</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>94.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>16.8</v>
+        <v>46.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.9</v>
+        <v>131.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81</v>
+        <v>814.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>14.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1065,73 +1067,71 @@
         <v>391.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>424.4</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>78</v>
+        <v>1718</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>29.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>27.4</v>
+        <v>0.2</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>84.5</v>
+        <v>0.8</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>18.9</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>87</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1147,70 +1147,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>149.7</v>
+        <v>1749.7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1289.5</v>
+        <v>12849.1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.5</v>
+        <v>55.8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>213.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1702.6</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>13.5</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
+        <v>13.3</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>17.7</v>
+      </c>
       <c r="L9" s="3" t="n">
-        <v>5.7</v>
+        <v>56.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>531.1</v>
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484912.4</v>
-      </c>
-      <c r="P9" s="3" t="n"/>
+        <v>1484.8</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>11.5</v>
+        <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>85.3</v>
+        <v>185.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.5</v>
+        <v>188.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>3.3</v>
+        <v>1233.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>935.9</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>184.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>46.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14154.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.8</v>
+        <v>119.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1229,72 +1235,70 @@
         <v>349.9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-4244 3
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>25.8</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="n">
-        <v>2.9</v>
+        <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>551.2</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>11</v>
+        <v>20.4</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>111</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>196.8</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2.3</v>
+        <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.2</v>
+        <v>17.9</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>12.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="U10" s="3" t="n"/>
+        <v>14167.1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V10" s="3" t="n">
-        <v>29.9</v>
+        <v>19</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>431.2</v>
+      <c r="X10" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>182.9</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>151</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1309,87 +1313,64 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="3" t="n">
+        <v>1509.3</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="G11" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24242
-22
-144561919
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>26.3</v>
+      <c r="Q11" s="8" t="n">
+        <v>226.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>12.1</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-741
-</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>40.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>17.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>660.1</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>9.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1405,63 +1386,77 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>93.90000000000001</v>
+        <v>1306.7</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>15</v>
+        <v>1.2</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>145</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="8" t="n">
+        <v>94.8</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M12" s="3" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>21.9</v>
+      </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V12" s="3" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>43.5</v>
+        <v>4.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>1092</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1476,76 +1471,66 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>357.9</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>18.3</v>
+        <v>1357.9</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="8" t="n">
+        <v>181.3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="H13" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>13.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="8" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>28.9</v>
-      </c>
+        <v>10.9</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>83.90000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
+      </c>
+      <c r="W13" s="8" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1561,72 +1546,70 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>11.8</v>
+        <v>153.2</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="8" t="n">
+        <v>1182</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>44.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n">
+      <c r="P14" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q14" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
+      <c r="R14" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>1.5</v>
+        <v>10.6</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>1.2</v>
+      <c r="W14" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.2</v>
+        <v>81811</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1642,74 +1625,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>639</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>372.1</v>
-      </c>
-      <c r="I15" s="3" t="n"/>
+        <v>10110.8</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>1181.5</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>13.2</v>
+      <c r="L15" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>30.1</v>
+        <v>21.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>13.3</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>22.6</v>
+        <v>0.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>3</v>
+        <v>17.9</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>16.5</v>
+        <v>12</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>116.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1724,73 +1707,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-7656
-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>2227.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>466.8</v>
+        <v>256.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.5</v>
+        <v>92.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>71.2</v>
+        <v>79.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.8</v>
+        <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.8</v>
+        <v>121.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L16" s="3" t="n"/>
+        <v>39.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>59.1</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>58.2</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>67.90000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>439.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="Q16" s="3" t="n">
-        <v>66.2</v>
+        <v>11191</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>82.2</v>
+        <v>0.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>7.7</v>
+        <v>721.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>310.1</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>160.9</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>385.2</v>
+        <v>921.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>89.2</v>
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>182.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369.9</v>
+        <v>1364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1806,84 +1793,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2224.9</v>
+        <v>245.9</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>44.4</v>
+        <v>11.8</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>59.1</v>
+        <v>29.4</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N17" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>4839</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>197.8</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-1
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-2
-</t>
-        </is>
+        <v>22.2</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>7.7</v>
+        <v>162</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>6.3</v>
+        <v>19.2</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>16.7</v>
+        <v>119.6</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.9</v>
+        <v>14.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1899,87 +1876,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>1435.8</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>20.9</v>
+      <c r="E18" s="8" t="n">
+        <v>244.4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>894.1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-7648
-</t>
-        </is>
-      </c>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>23.2</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>11.8</v>
+        <v>0.4</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>16.5</v>
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>61</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P18" s="3" t="n"/>
+        <v>99</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>15.4</v>
+        <v>72.3</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>115.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>456.2</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1238
-224
-</t>
-        </is>
+        <v>1406</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W18" s="8" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22254
-224
-1111
-</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>15.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>13791</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.4</v>
+        <v>110.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1995,74 +1959,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>1531.1</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>16.6</v>
+      <c r="E19" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
+        <v>3.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>4.4</v>
+        <v>10</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>711</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>32.9</v>
+        <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1132</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.4</v>
+        <v>261.1</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>64.2</v>
+        <v>24.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>48.5</v>
+        <v>0.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>0.3</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>14.6</v>
+        <v>21.2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>142</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2078,82 +2040,69 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.9</v>
+        <v>592.2</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>10.4</v>
+      <c r="E20" s="8" t="n">
+        <v>208.4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G20" s="3" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G20" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-2
-72
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.3</v>
+      <c r="H20" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>733.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>8818.1</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>51.3</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="8" t="n">
+        <v>151.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>42.5</v>
+        <v>140.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>17.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>2298.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2167,79 +2116,75 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-3894
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
+      <c r="C21" s="3" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>12.2</v>
+        <v>0.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>12.7</v>
+        <v>121.1</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.9</v>
+        <v>42.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>3.5</v>
+        <v>12.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.2</v>
+        <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>14.9</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1931</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V21" s="8" t="n">
-        <v>393.8</v>
+        <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2255,76 +2200,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
+        <v>1429</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>18.7</v>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="8" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>18.3</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N22" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N22" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>14.9</v>
+      <c r="S22" s="8" t="n">
+        <v>194.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>4.9</v>
+        <v>443454.4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>20</v>
+      <c r="W22" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1239.4</v>
+        <v>113.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2340,76 +2281,72 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>232.3</v>
+        <v>23203.1</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>13.2</v>
+        <v>132.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>561.1</v>
+        <v>551.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>759.4</v>
+        <v>750.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>141.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>12.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.3</v>
+        <v>101.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>12.3</v>
+        <v>1.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>14.5</v>
-      </c>
+        <v>61.8</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>2493</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>128.9</v>
+        <v>1128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.2</v>
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2357.1</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>4.2</v>
+        <v>188.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>16.7</v>
+        <v>1106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>215.6</v>
+        <v>185.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>13.9</v>
+        <v>26.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>34.5</v>
+        <v>1341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>60.9</v>
+        <v>141</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2425,7 +2362,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>46.4</v>
+        <v>484.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>26.4</v>
@@ -2433,68 +2370,64 @@
       <c r="E24" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G24" s="3" t="n">
+      <c r="F24" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G24" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>40.5</v>
+        <v>18.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.5</v>
+        <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>493</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>63.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="S24" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S24" s="8" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>88.5</v>
+        <v>1247.9</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>197.5</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>21.3</v>
+        <v>91.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>831.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>86.2</v>
+        <v>41.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>168.9</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2509,88 +2442,65 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4889
-49
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="C25" s="3" t="n">
+        <v>1488.9</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I25" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>24.7</v>
-      </c>
       <c r="R25" s="3" t="n">
-        <v>17.6</v>
+        <v>0.7</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>49.5</v>
+        <v>549.3</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>772.1</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292575
-111979
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2122
-1
-1111919
-</t>
-        </is>
+        <v>151.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>6.9</v>
+        <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>8.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2606,74 +2516,70 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>340.2</v>
+        <v>1349.9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.7</v>
+        <v>16.6</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>18.3</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="S26" s="8" t="n">
+        <v>547.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>63.5</v>
+        <v>163.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>15.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>63.9</v>
+        <v>21.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>1.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>55</v>
+        <v>512.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.1</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2692,76 +2598,62 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>6.6</v>
-      </c>
+        <v>211.4</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="8" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>29.1</v>
+        <v>2</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N27" s="3" t="n"/>
+        <v>42.4</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P27" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>16.2</v>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>161.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-11737
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78 277
-185
-</t>
-        </is>
+        <v>17.4</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>187.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2780,25 +2672,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>53.3</v>
+        <v>15139.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>21.5</v>
+        <v>27</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>111.5</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>45.4</v>
+        <v>4.1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>154.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.4</v>
+        <v>18.7</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
@@ -2806,51 +2698,43 @@
       <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>124.3</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-1554
-</t>
-        </is>
+      <c r="L28" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>13.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>19</v>
+      <c r="R28" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>99</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
       <c r="Y28" s="3" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.8</v>
@@ -2869,74 +2753,70 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>53.3</v>
+        <v>523.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>482.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+        <v>484.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.2</v>
+        <v>16.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>122.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>12</v>
+      <c r="R29" s="8" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>472.8</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>8.1</v>
-      </c>
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
       <c r="Y29" s="3" t="n">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>21.2</v>
+        <v>111.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2952,45 +2832,47 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>284.8</v>
+        <v>22848.1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>322.6</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>522.7</v>
+        <v>152.9</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>67.8</v>
+        <v>21.7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>29.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36.9</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.8</v>
+        <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.5</v>
+        <v>1119.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>13.5</v>
+        <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.7</v>
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4816.1</v>
-      </c>
-      <c r="P30" s="3" t="n"/>
+        <v>1489</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" s="3" t="n">
         <v>113.2</v>
       </c>
@@ -2998,28 +2880,28 @@
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>29.5</v>
+        <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>181.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>23.2</v>
+        <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>365</v>
+        <v>1365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35.9</v>
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3035,74 +2917,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>451</v>
+        <v>1452</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>19.3</v>
+      <c r="F31" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>1.3</v>
+        <v>39.1</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>2.8</v>
+        <v>97.8</v>
       </c>
       <c r="P31" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>40.4</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.3</v>
+      <c r="R31" s="8" t="n">
+        <v>179.3</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>0.5</v>
+      <c r="X31" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.8</v>
+        <v>730</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3118,71 +2996,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>520.9</v>
+        <v>520.8</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.5</v>
+        <v>27.9</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>110.2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>757.4</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>19.1</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>1.5</v>
+        <v>61.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>1090.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>103.3</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>97</v>
+        <v>97.8</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.1</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n">
-        <v>21.1</v>
+        <v>162.5</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3197,74 +3075,64 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3497.1</v>
+        <v>349.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>70.2</v>
+        <v>28.8</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>11.4</v>
+        <v>485.4</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>2111.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="K33" s="3" t="inlineStr"/>
       <c r="L33" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n">
-        <v>16.1</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>9.1</v>
+        <v>98.8</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>20.3</v>
+        <v>204.3</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S33" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="inlineStr"/>
       <c r="W33" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>18.7</v>
-      </c>
+        <v>44.4</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>189</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3280,76 +3148,72 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>18.5</v>
+        <v>44.3</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>4.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L34" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>29.1</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>181.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72</v>
+        <v>72.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W34" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>1287.1</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
-        <v>8582</v>
+        <v>893</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3365,19 +3229,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>56.7</v>
+        <v>1506.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>4</v>
+        <v>23.1</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>154</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9.5</v>
@@ -3386,54 +3250,52 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
+        <v>51.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>48.1</v>
-      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>17.6</v>
+      <c r="R35" s="8" t="n">
+        <v>147.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>520.6</v>
-      </c>
-      <c r="U35" s="3" t="n">
+        <v>572</v>
+      </c>
+      <c r="U35" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>846.3</v>
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>16.2</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>278.7</v>
+        <v>4116.8</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>68.5</v>
       </c>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Z35" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3448,18 +3310,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>26.3</v>
+        <v>535.5</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>56.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>12.8</v>
+        <v>0.9</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="G36" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3472,52 +3334,50 @@
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>12.6</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>17.1</v>
+        <v>25.5</v>
+      </c>
+      <c r="R36" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>0.2</v>
+        <v>685</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>434.3</v>
+      <c r="W36" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.2</v>
+        <v>1110.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3533,101 +3393,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-1188414042
-</t>
-        </is>
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>12.5</v>
+        <v>160.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614242
-149081
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-119019
-</t>
-        </is>
+        <v>991.7</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>146</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.7</v>
+        <v>116.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.8</v>
+        <v>81.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>422.7</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">714531 7
-</t>
-        </is>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
-        </is>
+        <v>2492</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>111818.5</v>
+        <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>8.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8.9</v>
+        <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3169.4</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>541.3</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">646257
-121191
-</t>
-        </is>
+        <v>1100.9</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>183.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>345.6</v>
+        <v>394.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3643,90 +3474,68 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>69</v>
+        <v>2448.1</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="J38" s="8" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-727227
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>17.6</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="n">
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.3</v>
+        <v>424.3</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-92
-</t>
-        </is>
+        <v>20.2</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>345.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3742,85 +3551,64 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>573.9</v>
+        <v>3599.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.2</v>
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1118</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>92</v>
+        <v>1980.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>18.4</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81556
-15252197
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>1720</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 28
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>12.5</v>
+        <v>21.2</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>8151.7</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>119.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3836,77 +3624,67 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-4
-</t>
-        </is>
+        <v>335.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>71</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>15.9</v>
+      <c r="G40" s="8" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>5.9</v>
+        <v>17.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>26.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.4</v>
+      <c r="S40" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>63.5</v>
+        <v>69.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="W40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>88.3</v>
+      <c r="X40" s="8" t="n">
+        <v>199.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>76</v>
+        <v>983</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3925,80 +3703,66 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5.2</v>
+        <v>245451.2</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>18.9</v>
+      <c r="E41" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>1281.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>5.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>51</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.2</v>
+        <v>818.5</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>97.2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22</v>
+        <v>23.9</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>717.9</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>214.2</v>
+        <v>121.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4014,87 +3778,67 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5724.4</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="8" t="n">
+        <v>60.1</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>12.8</v>
+        <v>19.3</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>251.7</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>5.7</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432
-5
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="U42" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>161.3</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4108,97 +3852,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>6666844.6</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>242.2</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717774
-82
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-8
-242257
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1859957
-5
-13 2
-529
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>2222.4</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4212,89 +3889,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>5724.4</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-0
-2644
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-21
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424622
-2224
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>2169.4</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4309,75 +3927,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>10197.9</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>41.8</v>
-      </c>
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="n">
-        <v>754.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>107.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>56.8</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>14.9</v>
+        <v>454.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>101.9</v>
+        <v>121.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.1</v>
+        <v>51.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>38</v>
+        <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
+        <v>198.6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>166</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>54.7</v>
+        <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22222.4</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.3</v>
+        <v>831.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
+        <v>168.3</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+        <v>8263</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>331.8</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4391,23 +4005,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>47.8</v>
-      </c>
+      <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F46" s="3" t="n">
+      <c r="E46" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>6.7</v>
+      <c r="G46" s="8" t="n">
+        <v>169.4</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>19.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>36.1</v>
@@ -4415,53 +4027,46 @@
       <c r="J46" s="3" t="n">
         <v>52.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="3" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>24.2</v>
+        <v>6</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>2169.4</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197 1
-</t>
-        </is>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>2261.5</v>
+      </c>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="W46" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>1680.1</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>391.2</v>
+        <v>3012.1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>27.9</v>
@@ -748,10 +748,10 @@
         <v>18.5</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>181.7</v>
+        <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -766,46 +766,46 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>19.9</v>
+        <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>114.1</v>
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>542.5</v>
+        <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="8" t="n">
-        <v>2219.1</v>
-      </c>
-      <c r="W4" s="8" t="n">
+      <c r="V4" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>41.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.1</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -823,68 +823,74 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>44.5</v>
+        <v>11.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>15.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
+        <v>29.5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>18.7</v>
+      </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S5" s="8" t="n">
+      <c r="R5" s="8" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="V5" s="8" t="n">
-        <v>189.5</v>
+        <v>199.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.2</v>
+        <v>19.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>2.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>66.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -902,68 +908,74 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1.4</v>
+        <v>69.5</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>101.1</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>411</v>
-      </c>
-      <c r="N6" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>2.3</v>
+      <c r="Q6" s="8" t="n">
+        <v>158.4</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="8" t="n">
-        <v>715.8</v>
+      <c r="U6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>114.3</v>
+        <v>18.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -979,76 +991,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1275.8</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>22.2</v>
+        <v>275.8</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2859.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>444.4</v>
+        <v>17.9</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>112.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.4</v>
+        <v>12.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>15</v>
+        <v>13.7</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>43.3</v>
+      <c r="S7" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="U7" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>8.4</v>
+      <c r="U7" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>131.3</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>814.9</v>
+        <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1064,22 +1076,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>26.1</v>
+        <v>291.2</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>26.3</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>10.5</v>
+        <v>109.5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8.1</v>
+        <v>18.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1088,50 +1100,52 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>424.4</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O8" s="3" t="n">
-        <v>1718</v>
+        <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>17.3</v>
+        <v>97.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>2.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.2</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1150,70 +1164,70 @@
         <v>1749.7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>12849.1</v>
+        <v>128.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>911.9</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1702.6</v>
+        <v>60.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>17.7</v>
+        <v>7.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.4</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>551.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>25.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1484.8</v>
+        <v>484.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.9</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>188.5</v>
+        <v>885.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>380.5</v>
+        <v>9501.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1233.3</v>
+        <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>184.9</v>
+        <v>8.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>911.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14154.5</v>
+        <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>119.8</v>
@@ -1232,15 +1246,17 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
+        <v>849.9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G10" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -1248,26 +1264,28 @@
         <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>797.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>1.5</v>
+        <v>96.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1276,28 +1294,28 @@
         <v>17.9</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>12.7</v>
+        <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>14167.1</v>
+        <v>26.7</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1313,12 +1331,14 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1509.3</v>
+        <v>909.3</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E11" s="8" t="n">
+        <v>47.9</v>
+      </c>
       <c r="F11" s="8" t="n">
         <v>19</v>
       </c>
@@ -1326,33 +1346,43 @@
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>84.7</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="8" t="n">
-        <v>4.2</v>
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>226.3</v>
+        <v>66.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.4</v>
+        <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>40.1</v>
+        <v>862</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
@@ -1360,17 +1390,17 @@
       <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>2.6</v>
+      <c r="W11" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1386,37 +1416,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1306.7</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>25.9</v>
+        <v>506.7</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.2</v>
+        <v>18.9</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>94.8</v>
+        <v>9.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>21.9</v>
+        <v>19.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1425,37 +1455,37 @@
         <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>4.2</v>
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>4.3</v>
+        <v>11.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1092</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1471,66 +1501,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1357.9</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+        <v>3514.9</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>111.2</v>
+      </c>
       <c r="F13" s="8" t="n">
-        <v>181.3</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>4.4</v>
+        <v>14.7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
       <c r="N13" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="P13" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>180.9</v>
+      </c>
       <c r="R13" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="X13" s="8" t="n">
+        <v>6816.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>9.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1546,70 +1586,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>153.2</v>
+        <v>25.5</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>181.3</v>
-      </c>
-      <c r="G14" s="8" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="8" t="n">
-        <v>1182</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>3</v>
+      <c r="I14" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P14" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>14.9</v>
+      <c r="P14" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>19.8</v>
+        <v>14.1</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U14" s="3" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>6</v>
+        <v>19.5</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>81811</v>
+        <v>28.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1625,19 +1671,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1631</v>
-      </c>
-      <c r="D15" s="8" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>10110.8</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>1181.5</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>15.8</v>
+      <c r="E15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1646,53 +1692,55 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>17.8</v>
+        <v>57.4</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>21.3</v>
+        <v>711.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+      <c r="P15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
+      <c r="R15" s="8" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>168</v>
+      </c>
       <c r="U15" s="3" t="n">
-        <v>17.9</v>
+        <v>15.8</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>6.4</v>
+        <v>2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>18.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1711,16 +1759,16 @@
         <v>2227.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>128</v>
+        <v>1298</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>256.8</v>
+        <v>56.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>92.3</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>79.2</v>
+        <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
@@ -1729,13 +1777,13 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>121.8</v>
+        <v>51.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>59.1</v>
+        <v>591.7</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
@@ -1744,40 +1792,40 @@
         <v>67.90000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>439.8</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11191</v>
+        <v>17119</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.1</v>
+        <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>721.1</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.1</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>921.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.9</v>
+        <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>182.2</v>
+        <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1364</v>
+        <v>2369.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>393.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1793,31 +1841,31 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>245.9</v>
+        <v>445.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>14.5</v>
+        <v>11.9</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>99.8</v>
+        <v>5.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
@@ -1827,25 +1875,25 @@
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>197.8</v>
-      </c>
-      <c r="P17" s="8" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>162</v>
+        <v>72.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>19.2</v>
+        <v>12.2</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>119.6</v>
@@ -1853,14 +1901,14 @@
       <c r="W17" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>14.4</v>
+      <c r="X17" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1876,56 +1924,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1435.8</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="8" t="n">
-        <v>244.4</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="E18" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>61.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>61</v>
+        <v>1610.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>72.3</v>
+      <c r="R18" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>115.4</v>
+        <v>101.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1406</v>
+        <v>9</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>17.9</v>
@@ -1933,17 +1983,17 @@
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>15.6</v>
+      <c r="W18" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>13791</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.9</v>
+        <v>11.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1959,69 +2009,73 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1531.1</v>
+        <v>95311.10000000001</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="I19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>211</v>
+        <v>11.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>711</v>
-      </c>
-      <c r="N19" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="N19" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="R19" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>24.2</v>
+        <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.3</v>
+        <v>94.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>21.2</v>
+      <c r="W19" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16.6</v>
@@ -2040,69 +2094,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>592.2</v>
+        <v>542.2</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>208.4</v>
+        <v>20.4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>114.3</v>
-      </c>
-      <c r="G20" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>733.5</v>
+        <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>111.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>8818.1</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>221.2</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>811</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
+        <v>98.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="S20" s="8" t="n">
-        <v>151.3</v>
+        <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>140.5</v>
+        <v>40.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>18.4</v>
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>89.5</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>2298.2</v>
+        <v>29.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2119,59 +2181,61 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0.4</v>
+      <c r="E21" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="G21" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>42.1</v>
+      <c r="H21" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>11.3</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>54.9</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S21" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>1931</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V21" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2181,10 +2245,10 @@
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2200,72 +2264,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1429</v>
+        <v>194828.8</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="F22" s="8" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>13.1</v>
+        <v>98.7</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>8</v>
+        <v>19.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>992</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R22" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>194.9</v>
+        <v>49.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>443454.4</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V22" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>13.9</v>
+      <c r="X22" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>505.9</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>113.4</v>
+        <v>1199.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2281,72 +2349,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23203.1</v>
+        <v>12320.8</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>132.1</v>
+        <v>112.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>551.4</v>
+        <v>201.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>750.9</v>
+        <v>75.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>141.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>101.3</v>
+        <v>5.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>61.8</v>
       </c>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>711.5</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1128.9</v>
+        <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>781.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>235.7</v>
+        <v>2351.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1106.7</v>
+        <v>106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>26.3</v>
+        <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1341.5</v>
+        <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>141</v>
+        <v>541</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2367,67 +2439,71 @@
       <c r="D24" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="G24" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="8" t="n">
-        <v>15.6</v>
+      <c r="S24" s="3" t="n">
+        <v>129.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1247.9</v>
+        <v>22.9</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>197.5</v>
+        <v>177.7</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>91.3</v>
+        <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>41.1</v>
+        <v>17.7</v>
       </c>
       <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.9</v>
+        <v>168.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2443,64 +2519,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="8" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="G25" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>107.9</v>
+        <v>6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>29.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0.7</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>549.3</v>
+        <v>6.9</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>151.8</v>
+        <v>13.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>16.9</v>
+        <v>116.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>16.8</v>
+        <v>116.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2516,52 +2604,58 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>25.6</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>8.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="M26" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>547.4</v>
+      <c r="R26" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>163.5</v>
+        <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2576,10 +2670,10 @@
         <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>512.1</v>
+        <v>194</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>211.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2597,66 +2691,74 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>211.4</v>
+      <c r="D27" s="8" t="n">
+        <v>2571.7</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="8" t="n">
-        <v>1144</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>15.1</v>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M27" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>161.8</v>
+        <v>1618.1</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>26.8</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>187.5</v>
+        <v>15859.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>113</v>
+        <v>913</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2672,72 +2774,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>15139.5</v>
-      </c>
-      <c r="D28" s="3" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>111.5</v>
+        <v>15.6</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.1</v>
+        <v>19.3</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>154.5</v>
+        <v>150.9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="8" t="n">
-        <v>13.4</v>
+      <c r="L28" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>113.3</v>
+        <v>13.3</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q28" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>99</v>
+      <c r="S28" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>11</v>
+      </c>
       <c r="Y28" s="3" t="n">
-        <v>121</v>
+        <v>1891</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2756,67 +2862,73 @@
         <v>523.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>484.1</v>
+        <v>18.8</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>16.2</v>
+      <c r="J29" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>910.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>122.4</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>181.7</v>
-      </c>
-      <c r="S29" s="8" t="n">
+        <v>517.1</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
+        <v>57.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.2</v>
+        <v>111.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2832,73 +2944,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.1</v>
+        <v>22848.3</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>131.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>152.9</v>
+        <v>52.7</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>21.7</v>
+        <v>91.7</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1119.5</v>
+        <v>119.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1489</v>
+        <v>9489</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>1113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>851.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>184.4</v>
+        <v>844.7</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
+        <v>35.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1365</v>
+        <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>35</v>
@@ -2917,55 +3029,61 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1452</v>
+        <v>1532</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>15.8</v>
+      <c r="F31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>14.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>412.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>40.4</v>
+      <c r="P31" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>179.3</v>
+        <v>12.5</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>211.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
@@ -2977,7 +3095,7 @@
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -2996,71 +3114,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>27.9</v>
+        <v>528</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>110.2</v>
+        <v>10.2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>217.7</v>
+        <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>61.2</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>1090.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>97.8</v>
+        <v>49</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R32" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="U32" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3077,62 +3201,74 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>28.8</v>
+      <c r="D33" s="8" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>485.4</v>
+        <v>18.9</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>2111.4</v>
+        <v>11.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>6.8</v>
+      </c>
       <c r="L33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>18.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>98.8</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>204.3</v>
+      <c r="Q33" s="8" t="n">
+        <v>203.5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>43.8</v>
+        <v>17.8</v>
       </c>
       <c r="S33" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="3" t="inlineStr"/>
+      <c r="V33" s="8" t="n">
+        <v>19.9</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3148,72 +3284,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.1</v>
+        <v>329.9</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>44.3</v>
+      <c r="E34" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>14.1</v>
+        <v>8.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>18.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>11.4</v>
+        <v>1.7</v>
       </c>
       <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="8" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q34" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>18.9</v>
+      <c r="R34" s="8" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="S34" s="8" t="n">
-        <v>181.8</v>
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72.8</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>29.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>1287.1</v>
+        <v>87.7</v>
       </c>
       <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="inlineStr"/>
+      <c r="X34" s="8" t="n">
+        <v>81</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>893</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3229,19 +3369,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1506.7</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F35" s="8" t="n">
+        <v>5056.7</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="8" t="n">
-        <v>154</v>
+      <c r="G35" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9.5</v>
@@ -3250,33 +3390,37 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>51.5</v>
+        <v>21.1</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>84.8</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>147.6</v>
+        <v>1891</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>572</v>
+        <v>252</v>
       </c>
       <c r="U35" s="8" t="n">
         <v>12.8</v>
@@ -3285,13 +3429,13 @@
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>16.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>4116.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.5</v>
+        <v>168.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3312,14 +3456,14 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>81.3</v>
+      <c r="D36" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>15.9</v>
@@ -3334,51 +3478,51 @@
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>12.6</v>
+      </c>
       <c r="O36" s="3" t="n">
         <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>14.8</v>
+      <c r="R36" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>65.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>685</v>
+        <v>115</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>1110.8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3393,72 +3537,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>2290.9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18.4</v>
+        <v>128.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>160.9</v>
+        <v>60.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>991.7</v>
+        <v>99.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.6</v>
+        <v>656.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>116.1</v>
+        <v>167.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>81.5</v>
+        <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>2492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.5</v>
+        <v>115.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>811.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>116.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>54.5</v>
+        <v>554.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1100.9</v>
+        <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>183.1</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>89.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>394.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3474,19 +3622,19 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2448.1</v>
+        <v>448.9</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="F38" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>135.1</v>
+        <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3495,47 +3643,53 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>984.9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>23.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>217.6</v>
+      </c>
       <c r="T38" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>424.3</v>
+        <v>83.5</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>16.6</v>
+        <v>116.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3551,64 +3705,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3599.9</v>
+        <v>5372.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1118</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K39" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>18.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1720</v>
+        <v>58146.9</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>21.2</v>
+        <v>12.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>8151.7</v>
+        <v>157.5</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>119.6</v>
+        <v>12.3</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5</v>
+        <v>141.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3624,67 +3788,71 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.1</v>
+        <v>52.5</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>27.2</v>
+        <v>21.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>17.3</v>
+      <c r="G40" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.4</v>
+        <v>21.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="8" t="n">
-        <v>18.5</v>
+      <c r="S40" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="W40" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>199.3</v>
+        <v>181.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>983</v>
+        <v>83</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3703,66 +3871,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>245451.2</v>
+        <v>458.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.4</v>
+        <v>12.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>1281.3</v>
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>51</v>
+        <v>51.9</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>818.5</v>
+        <v>88.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>717.9</v>
+        <v>17.4</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>216.6</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="8" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>222</v>
+        <v>16.6</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>4213.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>121.2</v>
+        <v>1112</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3778,39 +3956,43 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>524.4</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr"/>
+        <v>5254.4</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>27.2</v>
+      </c>
       <c r="E42" s="8" t="n">
-        <v>60.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>251.7</v>
+        <v>151.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.8</v>
@@ -3818,25 +4000,27 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>1.8</v>
+      <c r="R42" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>14.7</v>
+        <v>148.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>543.5</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>22</v>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -3852,7 +4036,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
@@ -3889,7 +4075,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
@@ -3929,68 +4117,72 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="F45" s="3" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>107.9</v>
+        <v>7.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>454.4</v>
+        <v>119.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>121.9</v>
+        <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>42.9</v>
+        <v>212.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>51.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>4.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>198.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>831.4</v>
+        <v>851.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>168.3</v>
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>8263</v>
+        <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.8</v>
+        <v>331.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4005,55 +4197,61 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="n">
+        <v>5417.8</v>
+      </c>
       <c r="D46" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F46" s="8" t="n">
+      <c r="E46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>169.4</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>19.7</v>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>52.1</v>
+        <v>3.6</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>52.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>10.7</v>
+        <v>41.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.8</v>
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>29.7</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>247.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S46" s="8" t="n">
-        <v>2261.5</v>
-      </c>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>654.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
@@ -4062,7 +4260,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr"/>
       <c r="Y46" s="3" t="n">
-        <v>1680.1</v>
+        <v>1860.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3012.1</v>
+        <v>301.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>27.9</v>
@@ -751,7 +751,7 @@
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -772,24 +772,24 @@
         <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>19.1</v>
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -805,7 +805,7 @@
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -832,8 +832,8 @@
       <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>15.9</v>
+      <c r="G5" s="8" t="n">
+        <v>59.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>7.9</v>
@@ -847,11 +847,11 @@
       <c r="K5" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>29.5</v>
+      <c r="L5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>19.4</v>
+        <v>8149.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -860,13 +860,13 @@
         <v>90</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="R5" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
@@ -874,14 +874,12 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="8" t="n">
-        <v>199.5</v>
+        <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>19.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -890,7 +888,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>66.5</v>
+        <v>469.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -915,13 +913,13 @@
         <v>10.9</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -930,13 +928,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>69.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>211</v>
+        <v>1.1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
@@ -948,10 +946,10 @@
         <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>11.6</v>
@@ -960,22 +958,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>18.3</v>
+        <v>24.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -993,11 +991,11 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>2859.5</v>
+      <c r="D7" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>17.9</v>
@@ -1006,13 +1004,13 @@
         <v>9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>112.9</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1027,27 +1025,27 @@
         <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>77.5</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1060,7 +1058,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1076,13 +1074,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
+        <v>391.2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>109.5</v>
+        <v>67.3</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>18.9</v>
@@ -1100,27 +1098,27 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>190.6</v>
+      <c r="M8" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R8" s="8" t="n">
+        <v>2719.4</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1135,8 +1133,8 @@
       <c r="V8" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1161,31 +1159,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>43927.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>911.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>60.6</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>56.7</v>
@@ -1194,10 +1192,10 @@
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>25.1</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484.8</v>
+        <v>684.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.6</v>
@@ -1209,28 +1207,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>885.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9501.5</v>
+        <v>3801.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>911.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>119.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1246,13 +1244,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>849.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>18.4</v>
@@ -1267,11 +1265,9 @@
         <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>797.4</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>418.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
@@ -1285,7 +1281,7 @@
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1297,10 +1293,10 @@
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>7.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
@@ -1315,7 +1311,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1331,7 +1327,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>909.3</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>27.3</v>
@@ -1340,7 +1336,7 @@
         <v>47.9</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>16.6</v>
@@ -1348,8 +1344,8 @@
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>84.7</v>
+      <c r="I11" s="3" t="n">
+        <v>4.7</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
@@ -1358,43 +1354,43 @@
         <v>0.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>66.5</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>862</v>
+        <v>512</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
@@ -1416,10 +1412,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>29.9</v>
+        <v>506.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>5.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
@@ -1427,38 +1423,38 @@
       <c r="F12" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>13</v>
+      <c r="G12" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>15.5</v>
@@ -1469,23 +1465,23 @@
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>4.6</v>
+      <c r="U12" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1501,49 +1497,49 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3514.9</v>
+        <v>357.9</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="F13" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="P13" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>180.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>17.3</v>
@@ -1552,7 +1548,7 @@
         <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1561,16 +1557,16 @@
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>6816.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>791.5</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1586,40 +1582,40 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25.5</v>
+        <v>29.5</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>185.3</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+      <c r="L14" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1627,23 +1623,21 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q14" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>19.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>6.2</v>
@@ -1652,10 +1646,10 @@
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>28.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1671,13 +1665,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1638</v>
+        <v>631</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>18.5</v>
@@ -1697,14 +1691,14 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>711.3</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1716,25 +1710,25 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>57.9</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>15.8</v>
+        <v>48</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>69.40000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
@@ -1759,13 +1753,13 @@
         <v>2227.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1298</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>56.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9.5</v>
+        <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>71.2</v>
@@ -1777,43 +1771,43 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>51.8</v>
+        <v>21.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>591.7</v>
+        <v>5.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>17119</v>
+        <v>1111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310.9</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>160.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>801.7</v>
@@ -1822,10 +1816,10 @@
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2369.8</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>393.9</v>
+        <v>33.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1846,23 +1840,23 @@
       <c r="D17" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>11.9</v>
+      <c r="E17" s="8" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>5.8</v>
+      <c r="J17" s="8" t="n">
+        <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
@@ -1878,7 +1872,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1886,20 +1880,20 @@
       <c r="R17" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>72.2</v>
+        <v>42</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>119.6</v>
+      <c r="V17" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
         <v>16.5</v>
@@ -1924,7 +1918,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.1</v>
+        <v>455.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>25.9</v>
@@ -1933,31 +1927,31 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>138</v>
+        <v>13.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>61.5</v>
+        <v>1666.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>1610.5</v>
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>19</v>
@@ -1969,31 +1963,31 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>101.4</v>
+        <v>110.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>11.6</v>
+        <v>110.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2003,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>95311.10000000001</v>
+        <v>531.9</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>28</v>
@@ -2018,7 +2012,7 @@
         <v>10.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>17.4</v>
@@ -2027,19 +2021,19 @@
         <v>7.2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>11.2</v>
+        <v>111.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>13</v>
@@ -2047,11 +2041,11 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>0.4</v>
+      <c r="P19" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18</v>
@@ -2060,7 +2054,7 @@
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>94.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>7.2</v>
@@ -2068,10 +2062,10 @@
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2099,11 +2093,11 @@
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>11.9</v>
+      <c r="E20" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.8</v>
@@ -2115,22 +2109,22 @@
         <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>111.2</v>
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>811</v>
+        <v>211</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98.2</v>
+        <v>198</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2141,7 +2135,7 @@
       <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
@@ -2154,13 +2148,13 @@
         <v>22.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>29.9</v>
+        <v>299.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>721</v>
+        <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.6</v>
@@ -2184,8 +2178,8 @@
       <c r="D21" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>29.8</v>
+      <c r="E21" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>18.7</v>
@@ -2194,13 +2188,13 @@
         <v>12.1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2212,7 +2206,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>54.9</v>
+        <v>15.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2230,7 +2224,7 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
@@ -2248,7 +2242,7 @@
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2264,31 +2258,31 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>194828.8</v>
+        <v>9489</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>12.1</v>
+      <c r="E22" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>82.8</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
@@ -2297,22 +2291,22 @@
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>992</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>49.5</v>
@@ -2327,13 +2321,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>13.8</v>
+        <v>53.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>505.9</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1199.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2349,19 +2343,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.8</v>
+        <v>12320.3</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>112.1</v>
+        <v>132.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>201.5</v>
+        <v>261.1</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2373,7 +2367,7 @@
         <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>2.5</v>
@@ -2382,7 +2376,7 @@
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>711.5</v>
+        <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>293</v>
@@ -2394,13 +2388,13 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>781.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2351.7</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>88.5</v>
@@ -2418,7 +2412,7 @@
         <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>541</v>
+        <v>41</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2434,7 +2428,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>484.1</v>
+        <v>2464.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>26.4</v>
@@ -2442,38 +2436,36 @@
       <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>15.1</v>
+      <c r="G24" s="8" t="n">
+        <v>57.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>29.4</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2482,25 +2474,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>129.6</v>
+        <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>177.7</v>
+        <v>177.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2519,40 +2511,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>428.9</v>
+        <v>1488.9</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="F25" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <v>16</v>
+      <c r="G25" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>15.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>49.7</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>5.4</v>
+        <v>19.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>18</v>
@@ -2560,35 +2552,35 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
+      <c r="Q25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>37.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>13.8</v>
+        <v>113.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>116.8</v>
+        <v>216.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2619,40 +2611,40 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>19.4</v>
+        <v>109.4</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="R26" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
@@ -2664,16 +2656,16 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>211.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2691,20 +2683,20 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="8" t="n">
-        <v>2571.7</v>
+      <c r="D27" s="3" t="n">
+        <v>25.7</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F27" s="8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>14</v>
+      <c r="G27" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2713,7 +2705,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="L27" s="8" t="n">
         <v>12.4</v>
@@ -2722,40 +2714,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>1618.1</v>
+        <v>1618.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>15859.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>913</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2774,51 +2766,51 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>313.3</v>
-      </c>
-      <c r="D28" s="8" t="n">
+        <v>513.3</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>150.9</v>
+        <v>156.5</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>935.4</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>12.1</v>
+      <c r="N28" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2830,17 +2822,17 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="8" t="n">
-        <v>645.4</v>
+      <c r="V28" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>11</v>
+        <v>817</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>1891</v>
+        <v>191</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>11.8</v>
@@ -2859,10 +2851,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>323.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.8</v>
+        <v>28.8</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>10.7</v>
@@ -2879,38 +2871,38 @@
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="8" t="n">
-        <v>25.2</v>
+      <c r="J29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>109.7</v>
+        <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>517.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2919,16 +2911,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>12.7</v>
+        <v>17.3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2944,7 +2936,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.3</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>131.2</v>
@@ -2959,7 +2951,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
@@ -2971,34 +2963,32 @@
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>51.2</v>
+        <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>9489</v>
+        <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1113.2</v>
+        <v>113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>851.7</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>844.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3029,7 +3019,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1532</v>
+        <v>432</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.2</v>
@@ -3044,7 +3034,7 @@
         <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
@@ -3052,50 +3042,48 @@
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>412.8</v>
+        <v>11.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="V31" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
-        <v>16.4</v>
+      <c r="W31" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3114,10 +3102,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>528</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>28.9</v>
+        <v>5280.8</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>10.2</v>
@@ -3125,17 +3113,17 @@
       <c r="F32" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -3144,33 +3132,33 @@
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3180,10 +3168,10 @@
         <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3201,26 +3189,26 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="8" t="n">
-        <v>46.2</v>
+      <c r="D33" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>18.9</v>
+      <c r="F33" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>11.6</v>
+        <v>111.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>95.90000000000001</v>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>6.8</v>
@@ -3229,46 +3217,46 @@
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.6</v>
+        <v>11.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>203.5</v>
+      <c r="Q33" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3290,7 +3278,7 @@
         <v>23.3</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>19</v>
@@ -3298,29 +3286,29 @@
       <c r="G34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>19.7</v>
+      <c r="H34" s="8" t="n">
+        <v>49.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>71.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>18.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3328,8 +3316,8 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="R34" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>18.7</v>
@@ -3338,22 +3326,22 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>81</v>
+      <c r="X34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3369,12 +3357,12 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5056.7</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E35" s="8" t="n">
+        <v>506.7</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="F35" s="3" t="n">
@@ -3390,7 +3378,7 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>21.1</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3401,17 +3389,17 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>84.8</v>
+      <c r="N35" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1891</v>
+        <v>189</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>38.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>17.6</v>
@@ -3420,7 +3408,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="U35" s="8" t="n">
         <v>12.8</v>
@@ -3429,13 +3417,13 @@
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>67.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>168.5</v>
+        <v>683.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3460,12 +3448,12 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>10.5</v>
+        <v>105.4</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G36" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3486,11 +3474,11 @@
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>12.6</v>
+      <c r="N36" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.1</v>
@@ -3501,11 +3489,11 @@
       <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>65.8</v>
+      <c r="S36" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="U36" s="8" t="n">
         <v>17.9</v>
@@ -3513,14 +3501,14 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="8" t="n">
-        <v>14.6</v>
+      <c r="W36" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3537,7 +3525,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2290.9</v>
+        <v>2140.4</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>128.5</v>
@@ -3549,13 +3537,13 @@
         <v>99.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>656.6</v>
+        <v>672.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>167.9</v>
+        <v>141.7</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
@@ -3564,49 +3552,49 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>64.5</v>
+        <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.9</v>
+        <v>185.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>811.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>116.9</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>554.5</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>89.8</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>3.9</v>
+        <v>39.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3622,12 +3610,12 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.9</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="F38" s="3" t="n">
@@ -3642,24 +3630,24 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>20.1</v>
+      <c r="J38" s="3" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>2.8</v>
+        <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>984.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
@@ -3668,25 +3656,25 @@
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>217.6</v>
+        <v>127.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>83.5</v>
+        <v>23.3</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3705,23 +3693,23 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5372.9</v>
+        <v>579.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3733,16 +3721,16 @@
         <v>12.7</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
@@ -3751,10 +3739,10 @@
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58146.9</v>
+        <v>92.5</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>18</v>
@@ -3763,7 +3751,7 @@
         <v>12.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>157.5</v>
+        <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>12.3</v>
@@ -3772,7 +3760,7 @@
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>141.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3788,25 +3776,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>52.5</v>
+        <v>35.5</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>21.4</v>
+        <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
@@ -3825,19 +3813,19 @@
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3846,16 +3834,16 @@
         <v>12.7</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>181.3</v>
+        <v>181.5</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3871,25 +3859,21 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.6</v>
-      </c>
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51.9</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
@@ -3898,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
@@ -3916,13 +3900,13 @@
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S41" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>4213.5</v>
+        <v>423.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3931,16 +3915,16 @@
         <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1112</v>
+        <v>19.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3956,25 +3940,25 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5254.4</v>
+        <v>529.4</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="E42" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>151.7</v>
+        <v>1351.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>15.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -3982,13 +3966,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4001,24 +3985,24 @@
         <v>26.6</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>148.7</v>
+        <v>12.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>153.2</v>
+        <v>43.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
+      <c r="V42" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4118,22 +4102,22 @@
         <v>1911.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>109.7</v>
+        <v>1091.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>41.8</v>
+        <v>61.8</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.9</v>
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.4</v>
+        <v>119.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
@@ -4142,19 +4126,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>212.9</v>
+        <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4169,20 +4153,22 @@
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>831.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>67.5</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>200.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
         <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.9</v>
+        <v>2331.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4198,7 +4184,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5417.8</v>
+        <v>417.8</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>27.4</v>
@@ -4218,15 +4204,15 @@
       <c r="I46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>52.4</v>
+      <c r="J46" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>41.1</v>
+        <v>11181.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4238,29 +4224,29 @@
         <v>6.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>24.7</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>654.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
-      </c>
+        <v>54.1</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Y46" s="3" t="n">
-        <v>1860.8</v>
+        <v>1862.4</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>301.2</v>
+        <v>391.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>27.9</v>
@@ -744,14 +744,14 @@
       <c r="E4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>18.5</v>
+      <c r="F4" s="8" t="n">
+        <v>81.5</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -760,22 +760,22 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>11.9</v>
+      <c r="N4" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
@@ -784,10 +784,10 @@
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>14.1</v>
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>462.5</v>
+        <v>42.5</v>
       </c>
       <c r="U4" s="8" t="n">
         <v>19.1</v>
@@ -798,14 +798,14 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -832,11 +832,11 @@
       <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>59.4</v>
+      <c r="G5" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -845,13 +845,13 @@
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>8149.4</v>
+        <v>119.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -862,7 +862,7 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -874,12 +874,14 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="V5" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -888,7 +890,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>469.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -909,17 +911,17 @@
       <c r="D6" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>10.9</v>
+      <c r="E6" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -928,12 +930,12 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M6" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -952,22 +954,22 @@
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>24.6</v>
+      <c r="W6" s="8" t="n">
+        <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
@@ -1003,44 +1005,44 @@
       <c r="G7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>12.9</v>
+      <c r="H7" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>5</v>
+        <v>23.7</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>17.7</v>
+      <c r="S7" s="3" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
@@ -1051,14 +1053,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1076,11 +1078,11 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>67.3</v>
+      <c r="D8" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>18.9</v>
@@ -1089,7 +1091,7 @@
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1107,36 +1109,36 @@
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>2719.4</v>
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
+      <c r="V8" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="X8" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>43927.4</v>
+        <v>1749.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
@@ -1171,46 +1173,44 @@
         <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12.6</v>
+        <v>140.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>55.2</v>
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>766.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>684.8</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>9.6</v>
-      </c>
+        <v>484.9</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>85.3</v>
+        <v>185.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3801.5</v>
+        <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
@@ -1219,13 +1219,13 @@
         <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.4</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9414.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
+        <v>8349.9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.8</v>
@@ -1265,13 +1265,13 @@
         <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>418.1</v>
+        <v>9.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -1281,27 +1281,27 @@
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S10" s="8" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1310,9 +1310,7 @@
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="Z10" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1329,17 +1327,17 @@
       <c r="C11" s="3" t="n">
         <v>509.3</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>47.9</v>
+      <c r="E11" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>16.6</v>
+        <v>18.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
@@ -1351,22 +1349,22 @@
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.2</v>
+        <v>26</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>17.4</v>
+        <v>11.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.2</v>
+        <v>11.8</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="8" t="n">
         <v>26.3</v>
@@ -1375,25 +1373,25 @@
         <v>17.1</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>512</v>
-      </c>
-      <c r="U11" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U11" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>19.6</v>
+      <c r="X11" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1412,37 +1410,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>5.9</v>
+        <v>508.7</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>191.7</v>
+      <c r="L12" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>22.1</v>
+        <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1456,7 +1454,7 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="S12" s="8" t="n">
@@ -1472,13 +1470,13 @@
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1512,25 +1510,25 @@
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>21.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>23.6</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
@@ -1538,29 +1536,29 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="8" t="n">
-        <v>80.90000000000001</v>
+      <c r="Q13" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>11.8</v>
+        <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>185.4</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>791.5</v>
+        <v>17.8</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>29.1</v>
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
@@ -1585,34 +1583,34 @@
         <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G14" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>15.8</v>
+      <c r="I14" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>14.8</v>
@@ -1621,26 +1619,28 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>197</v>
+      </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="8" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>6.2</v>
+      <c r="V14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>16.2</v>
       </c>
       <c r="X14" s="8" t="n">
         <v>16</v>
@@ -1649,7 +1649,7 @@
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1671,13 +1671,13 @@
         <v>26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15.6</v>
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>50.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1692,7 +1692,7 @@
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>27.4</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
@@ -1710,19 +1710,19 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>2</v>
+        <v>17.8</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>16.3</v>
@@ -1734,7 +1734,7 @@
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1749,14 +1749,12 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2227.1</v>
-      </c>
+      <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
         <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>56.8</v>
+        <v>568.1</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92.5</v>
@@ -1768,7 +1766,7 @@
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>21.8</v>
@@ -1783,10 +1781,10 @@
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>57.1</v>
+        <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>399</v>
+        <v>489.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1798,28 +1796,28 @@
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.9</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
+        <v>603.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>9.5</v>
+        <v>958.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.7</v>
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1840,8 +1838,8 @@
       <c r="D17" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="8" t="n">
-        <v>99.40000000000001</v>
+      <c r="E17" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>18.5</v>
@@ -1855,14 +1853,14 @@
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>871.8</v>
+      <c r="J17" s="3" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="8" t="n">
@@ -1872,37 +1870,37 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>42</v>
+        <v>362</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>12.2</v>
+        <v>18.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="X17" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>872.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1918,7 +1916,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.5</v>
+        <v>845.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>25.9</v>
@@ -1926,17 +1924,17 @@
       <c r="E18" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>11.8</v>
+      <c r="F18" s="8" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1945,16 +1943,16 @@
         <v>0.1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>1666.6</v>
+        <v>24.4</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
@@ -1963,13 +1961,13 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>17.3</v>
+        <v>12.5</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>110.4</v>
+        <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="U18" s="8" t="n">
         <v>17.9</v>
@@ -1977,17 +1975,17 @@
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="X18" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2003,19 +2001,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.9</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2029,10 +2027,10 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
+      <c r="L19" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2041,8 +2039,8 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>9.4</v>
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>25.9</v>
@@ -2054,7 +2052,7 @@
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>7.2</v>
@@ -2072,7 +2070,7 @@
         <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2093,8 +2091,8 @@
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>80.5</v>
+      <c r="E20" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>19.3</v>
@@ -2106,25 +2104,25 @@
         <v>6.9</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="N20" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="N20" s="8" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2136,28 +2134,28 @@
         <v>18.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>22.4</v>
+      <c r="U20" s="8" t="n">
+        <v>222.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>299.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2178,38 +2176,38 @@
       <c r="D21" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>12.9</v>
+      <c r="E21" s="8" t="n">
+        <v>2.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>15.9</v>
+      <c r="N21" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2224,10 +2222,10 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>19.8</v>
@@ -2235,14 +2233,14 @@
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>20</v>
+      <c r="X21" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2258,40 +2256,40 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9489</v>
+        <v>989</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>18.7</v>
+        <v>26.9</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>11.2</v>
+        <v>8</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2305,11 +2303,11 @@
       <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>49.7</v>
+      <c r="S22" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>49.5</v>
+        <v>149.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2317,11 +2315,11 @@
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>53.8</v>
+      <c r="X22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
@@ -2343,28 +2341,28 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.3</v>
+        <v>2322.3</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>132.1</v>
+        <v>112.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>261.1</v>
+        <v>50.1</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.3</v>
@@ -2373,25 +2371,25 @@
         <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>2493</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2428,7 +2426,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2464.1</v>
+        <v>464.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>26.4</v>
@@ -2437,29 +2435,31 @@
         <v>11.3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>18.9</v>
+        <v>1.8</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>57.1</v>
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>11.9</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2470,29 +2470,29 @@
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>177.1</v>
+        <v>47.9</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X24" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>58.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2511,31 +2511,31 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
+        <v>488.9</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>13.6</v>
+      <c r="G25" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>49.7</v>
+        <v>4.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>10.7</v>
@@ -2543,35 +2543,35 @@
       <c r="M25" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>19.4</v>
+      <c r="N25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>18</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="8" t="n">
-        <v>41.5</v>
+      <c r="Q25" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>37.6</v>
+        <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1.9</v>
+        <v>13.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>113.2</v>
+        <v>49.5</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>216.9</v>
+        <v>16.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2611,10 +2611,10 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>23.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
@@ -2623,19 +2623,19 @@
         <v>0.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="M26" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
@@ -2643,14 +2643,14 @@
       <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="S26" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>21.6</v>
@@ -2659,10 +2659,10 @@
         <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>111.8</v>
@@ -2687,7 +2687,7 @@
         <v>25.7</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>17.1</v>
+        <v>11.7</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>18.1</v>
@@ -2702,34 +2702,34 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>1618.2</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>11.2</v>
+      <c r="R27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
@@ -2741,13 +2741,13 @@
         <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>0.7</v>
+        <v>16.7</v>
       </c>
       <c r="X27" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>23</v>
+        <v>1213</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2772,34 +2772,34 @@
         <v>27</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>156.5</v>
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>935.4</v>
+        <v>5.5</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.2</v>
+        <v>1.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>99</v>
@@ -2810,7 +2810,7 @@
       <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2823,13 +2823,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>817</v>
+        <v>17.8</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>191</v>
@@ -2851,19 +2851,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>323.3</v>
+        <v>523.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>18.1</v>
+      <c r="G29" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2877,29 +2877,29 @@
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>181.7</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>12</v>
+        <v>18.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>47.8</v>
@@ -2914,13 +2914,13 @@
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>1.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>112.9</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
+        <v>228.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>131.2</v>
+        <v>13.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>52.7</v>
+        <v>527.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>91.7</v>
@@ -2951,16 +2951,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>19.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>113.5</v>
+        <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>57.2</v>
@@ -2968,7 +2968,9 @@
       <c r="M30" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O30" s="3" t="n">
         <v>489</v>
       </c>
@@ -2976,7 +2978,7 @@
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>413.2</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>86.7</v>
@@ -2988,7 +2990,7 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
+        <v>35.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3019,44 +3021,44 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>10.4</v>
+      <c r="E31" s="8" t="n">
+        <v>101.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>58.4</v>
+        <v>18.3</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>39.1</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
@@ -3068,25 +3070,25 @@
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>16.9</v>
+      <c r="W31" s="8" t="n">
+        <v>16.4</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>730</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3102,12 +3104,12 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5280.8</v>
+        <v>520</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="F32" s="8" t="n">
@@ -3117,47 +3119,45 @@
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>20.1</v>
+      <c r="L32" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>21.1</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>264.6</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+        <v>62.6</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
@@ -3165,13 +3165,11 @@
         <v>17.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>170</v>
-      </c>
+        <v>17.2</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>171.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3195,17 +3193,17 @@
       <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>28.9</v>
+      <c r="F33" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>111.4</v>
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3214,49 +3212,49 @@
         <v>6.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.5</v>
+        <v>14.2</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R33" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>29.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>19.4</v>
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3281,34 +3279,34 @@
         <v>14.7</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>49.7</v>
+        <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>71.5</v>
+        <v>11.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="L34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.7</v>
+      <c r="N34" s="8" t="n">
+        <v>7.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>991</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3319,26 +3317,26 @@
       <c r="R34" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="8" t="n">
+      <c r="S34" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="8" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3383,20 +3381,20 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.2</v>
+        <v>12.9</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>189</v>
+        <v>399</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
@@ -3404,26 +3402,26 @@
       <c r="R35" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U35" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>683.5</v>
+        <v>68.3</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3448,10 +3446,10 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>105.4</v>
+        <v>10.9</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>15.9</v>
@@ -3460,57 +3458,59 @@
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>10.6</v>
+        <v>10</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R36" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>15.8</v>
+      <c r="S36" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>17.9</v>
+        <v>63</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>11.3</v>
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>3.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2140.4</v>
+        <v>2240.4</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>128.5</v>
@@ -3534,28 +3534,28 @@
         <v>60.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>99.2</v>
+        <v>94.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>672.6</v>
+        <v>62.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>141.7</v>
+        <v>14.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
@@ -3563,14 +3563,12 @@
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="P37" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="3" t="n">
-        <v>185.9</v>
+        <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
@@ -3585,16 +3583,16 @@
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>837.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.5</v>
+        <v>359.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.4</v>
+        <v>34.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3610,7 +3608,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
+        <v>44.8</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>25.7</v>
@@ -3621,7 +3619,7 @@
       <c r="F38" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3630,51 +3628,51 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>90.09999999999999</v>
+      <c r="J38" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>298.9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>127.6</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>19.9</v>
+        <v>128.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3701,15 +3699,17 @@
       <c r="E39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I39" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3717,14 +3717,14 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>12.7</v>
+      <c r="L39" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>1.7</v>
+        <v>12.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3732,35 +3732,33 @@
       <c r="P39" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>18</v>
+        <v>45.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>12.3</v>
+        <v>51.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>11.6</v>
+        <v>176</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3776,10 +3774,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.5</v>
+        <v>335.9</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>10.7</v>
@@ -3788,44 +3786,46 @@
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.5</v>
+      <c r="S40" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.5</v>
+        <v>169.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3834,16 +3834,16 @@
         <v>12.7</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="X40" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y40" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="Y40" s="3" t="n">
-        <v>89</v>
-      </c>
       <c r="Z40" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3861,17 +3861,21 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="D41" s="8" t="n">
+        <v>289.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="F41" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>51</v>
+      </c>
       <c r="I41" s="3" t="n">
         <v>0.3</v>
       </c>
@@ -3882,31 +3886,31 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>423.5</v>
+        <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3914,17 +3918,17 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="8" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>16.3</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.8</v>
+        <v>15.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3940,25 +3944,25 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>529.4</v>
+        <v>524.4</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>22.1</v>
+        <v>1.1</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="8" t="n">
-        <v>1351.7</v>
+      <c r="G42" s="3" t="n">
+        <v>125.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -3967,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -3985,26 +3989,22 @@
         <v>26.6</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>87.59999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>12.7</v>
+        <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="U42" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="8" t="n">
+      <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4099,46 +4099,46 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
+        <v>1981.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1091.7</v>
+        <v>109.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>61.8</v>
+        <v>41.8</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>107.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.9</v>
+        <v>16.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>44</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>31.6</v>
+        <v>5.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4150,7 +4150,7 @@
         <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.9</v>
+        <v>216.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>59</v>
@@ -4159,16 +4159,16 @@
         <v>831.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>200.8</v>
+        <v>62.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1263</v>
+        <v>263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2331.8</v>
+        <v>35.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>417.8</v>
+        <v>477.8</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>27.4</v>
@@ -4192,27 +4192,29 @@
       <c r="E46" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.6</v>
+        <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L46" s="8" t="n">
-        <v>11181.9</v>
+        <v>111.7</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4226,16 +4228,18 @@
       <c r="Q46" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>11.6</v>
+      <c r="R46" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>54.1</v>
       </c>
-      <c r="U46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
@@ -4243,10 +4247,10 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>1.4</v>
+        <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1862.4</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -744,14 +744,14 @@
       <c r="E4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>81.7</v>
+      <c r="F4" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -760,13 +760,13 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.4</v>
@@ -775,21 +775,21 @@
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>19.1</v>
+      <c r="S4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -798,7 +798,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -836,7 +836,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -850,8 +850,8 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>119.4</v>
+      <c r="M5" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -877,7 +877,7 @@
       <c r="U5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -890,7 +890,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
       <c r="D6" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="E6" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15</v>
@@ -927,27 +927,27 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -960,22 +960,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>12.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>9</v>
@@ -1012,25 +1012,25 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
+        <v>21.1</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="8" t="n">
+      <c r="M7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>19.3</v>
@@ -1039,10 +1039,10 @@
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
@@ -1053,14 +1053,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1117,8 +1117,8 @@
       <c r="P8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>27.4</v>
+      <c r="Q8" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.4</v>
@@ -1127,18 +1127,18 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
@@ -1173,10 +1173,10 @@
         <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1191,7 +1191,7 @@
         <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>551.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1204,10 +1204,10 @@
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.3</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1225,7 +1225,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.8</v>
@@ -1264,8 +1264,8 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
@@ -1274,7 +1274,7 @@
       <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1287,13 +1287,13 @@
         <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>117.7</v>
+        <v>17.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.7</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>509.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>27.3</v>
@@ -1333,29 +1333,29 @@
       <c r="E11" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>18.6</v>
+      <c r="G11" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1366,19 +1366,19 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="3" t="n">
@@ -1387,7 +1387,7 @@
       <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>25.9</v>
@@ -1418,28 +1418,28 @@
       <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="G12" s="8" t="n">
+      <c r="F12" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1454,29 +1454,29 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="8" t="n">
-        <v>12.9</v>
+      <c r="S12" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1500,7 +1500,7 @@
       <c r="D13" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1510,13 +1510,13 @@
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1525,9 +1525,9 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1546,18 +1546,18 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>185.4</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X13" s="8" t="n">
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1585,10 +1585,10 @@
       <c r="D14" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1597,19 +1597,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
+        <v>6.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1619,19 +1619,19 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
@@ -1639,10 +1639,10 @@
       <c r="V14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="W14" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>631</v>
+        <v>31</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>50.8</v>
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1686,19 +1686,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1709,19 +1709,19 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V15" s="8" t="n">
+      <c r="U15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1754,7 +1754,7 @@
         <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>568.1</v>
+        <v>56.8</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92.5</v>
@@ -1775,7 +1775,7 @@
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5.9</v>
+        <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
@@ -1784,13 +1784,13 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1111</v>
+        <v>111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
@@ -1799,16 +1799,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>958.2</v>
+        <v>98.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.9</v>
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1851,38 +1851,38 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>362</v>
+        <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>18.2</v>
@@ -1890,17 +1890,17 @@
       <c r="V17" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="8" t="n">
-        <v>16.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>872.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>25.9</v>
@@ -1924,17 +1924,17 @@
       <c r="E18" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>13</v>
+      <c r="F18" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1942,13 +1942,13 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>24.4</v>
+      <c r="L18" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
@@ -1961,25 +1961,25 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>19.6</v>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>59</v>
@@ -2013,7 +2013,7 @@
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2054,8 +2054,8 @@
       <c r="T19" s="3" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>7.2</v>
+      <c r="U19" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
@@ -2091,10 +2091,10 @@
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="E20" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2103,11 +2103,11 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
@@ -2115,23 +2115,23 @@
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>214</v>
-      </c>
-      <c r="N20" s="8" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>15.3</v>
@@ -2139,16 +2139,16 @@
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="8" t="n">
-        <v>222.4</v>
+      <c r="U20" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="8" t="n">
+      <c r="W20" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
@@ -2176,11 +2176,11 @@
       <c r="D21" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>2.7</v>
+      <c r="E21" s="3" t="n">
+        <v>12.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>12.1</v>
@@ -2197,7 +2197,7 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2207,7 +2207,7 @@
         <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2225,7 +2225,7 @@
         <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>19.8</v>
@@ -2233,8 +2233,8 @@
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>0.9</v>
+      <c r="X21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2256,22 +2256,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>9</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>26.9</v>
+      <c r="E22" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2280,16 +2280,16 @@
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2307,7 +2307,7 @@
         <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>149.5</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2318,14 +2318,14 @@
       <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="X22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+        <v>13.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2341,28 +2341,28 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
+        <v>2320.3</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>112.1</v>
+        <v>132.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>50.1</v>
+        <v>56.7</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
+        <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.3</v>
@@ -2371,25 +2371,25 @@
         <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>93</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2431,13 +2431,13 @@
       <c r="D24" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G24" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2447,7 +2447,7 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>1.4</v>
@@ -2459,7 +2459,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2470,23 +2470,23 @@
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>17.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>17.2</v>
@@ -2522,8 +2522,8 @@
       <c r="F25" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <v>10.9</v>
+      <c r="G25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
@@ -2535,31 +2535,31 @@
         <v>4.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>10.7</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2570,10 +2570,10 @@
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.4</v>
@@ -2613,8 +2613,8 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="8" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
@@ -2622,41 +2622,41 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>14.2</v>
@@ -2665,7 +2665,7 @@
         <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2684,16 +2684,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>11.7</v>
+        <v>25.1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>24</v>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2702,10 +2702,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>12.4</v>
@@ -2722,20 +2722,20 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.4</v>
@@ -2743,11 +2743,11 @@
       <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2771,17 +2771,17 @@
       <c r="D28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>15.9</v>
+      <c r="G28" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2793,9 +2793,9 @@
         <v>5.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2828,14 +2828,14 @@
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>17.8</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2851,19 +2851,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2887,15 +2887,15 @@
         <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2914,10 +2914,10 @@
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>11.2</v>
@@ -2939,10 +2939,10 @@
         <v>228.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>13.1</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>527.1</v>
+        <v>52.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>91.7</v>
@@ -2966,7 +2966,7 @@
         <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.7</v>
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -2987,10 +2987,10 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>314.8</v>
+        <v>14.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>101.9</v>
+        <v>25.2</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>18.3</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
@@ -3063,32 +3063,32 @@
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>111.4</v>
+      <c r="U31" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3112,8 +3112,8 @@
       <c r="E32" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>19.9</v>
+      <c r="F32" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.7</v>
@@ -3128,15 +3128,15 @@
         <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.5</v>
+        <v>10.5</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3145,17 +3145,17 @@
       <c r="P32" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q32" s="8" t="n">
-        <v>264.6</v>
-      </c>
-      <c r="R32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="n">
@@ -3164,12 +3164,12 @@
       <c r="W32" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>17.2</v>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3190,20 +3190,20 @@
       <c r="D33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3215,10 +3215,10 @@
         <v>14.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.5</v>
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3229,7 +3229,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3239,15 +3239,15 @@
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3270,28 +3270,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>89</v>
+      <c r="F34" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
@@ -3302,8 +3302,8 @@
       <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3324,15 +3324,15 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
@@ -3391,7 +3391,7 @@
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
@@ -3402,26 +3402,26 @@
       <c r="R35" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3445,8 +3445,8 @@
       <c r="D36" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>10.9</v>
+      <c r="E36" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>18.3</v>
@@ -3458,25 +3458,25 @@
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>8.6</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -3484,17 +3484,17 @@
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>19.8</v>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
@@ -3502,8 +3502,8 @@
       <c r="W36" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>3.3</v>
+      <c r="X36" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>55</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224.4</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>128.5</v>
@@ -3537,22 +3537,22 @@
         <v>94.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>64.2</v>
@@ -3561,20 +3561,20 @@
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="3" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>16.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3589,7 +3589,7 @@
         <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>25.7</v>
@@ -3628,10 +3628,12 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>13</v>
       </c>
@@ -3642,7 +3644,7 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>298.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
@@ -3650,17 +3652,17 @@
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="8" t="n">
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>128.9</v>
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
@@ -3668,11 +3670,11 @@
       <c r="W38" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3696,20 +3698,20 @@
       <c r="D39" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3718,21 +3720,21 @@
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3740,16 +3742,16 @@
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>51.7</v>
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>14.6</v>
@@ -3758,7 +3760,7 @@
         <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3774,7 +3776,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>27.2</v>
@@ -3803,17 +3805,17 @@
       <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>22</v>
@@ -3821,22 +3823,22 @@
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="8" t="n">
+      <c r="S40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>169.5</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y40" s="3" t="n">
@@ -3861,26 +3863,26 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="8" t="n">
-        <v>289.4</v>
+      <c r="D41" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3892,21 +3894,21 @@
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3918,8 +3920,8 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="8" t="n">
-        <v>181.5</v>
+      <c r="W41" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>16.3</v>
@@ -3956,13 +3958,13 @@
         <v>19.3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>125.7</v>
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -3971,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -3986,18 +3988,18 @@
         <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R42" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="V42" s="3" t="n">
@@ -4099,7 +4101,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
+        <v>1911.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>109.7</v>
@@ -4111,19 +4113,19 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>107.9</v>
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>44</v>
@@ -4138,7 +4140,7 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4156,13 +4158,13 @@
         <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>831.9</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4192,7 +4194,7 @@
       <c r="E46" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4205,13 +4207,13 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>111.7</v>
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>111100</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>10.7</v>
@@ -4220,10 +4222,10 @@
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>24.7</v>
@@ -4231,7 +4233,7 @@
       <c r="R46" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="8" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4250,10 +4252,10 @@
         <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>265.7</v>
+        <v>65.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.1</v>
@@ -881,7 +881,7 @@
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -890,7 +890,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -960,7 +960,7 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
@@ -1012,7 +1012,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
@@ -1207,7 +1207,7 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1225,7 +1225,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1287,7 +1287,7 @@
         <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.1</v>
+        <v>27.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>27.3</v>
@@ -1373,7 +1373,7 @@
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>14.4</v>
+        <v>26.8</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>42</v>
@@ -1391,7 +1391,7 @@
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1464,19 +1464,19 @@
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>14.7</v>
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1513,7 +1513,7 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
@@ -1534,7 +1534,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>18.9</v>
@@ -1546,7 +1546,7 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1601,13 +1601,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
+        <v>11.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1640,7 +1640,7 @@
         <v>14.5</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31</v>
+        <v>631</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26</v>
@@ -1754,7 +1754,7 @@
         <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>56.8</v>
+        <v>568.8</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92.5</v>
@@ -1784,7 +1784,7 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1854,7 +1854,7 @@
         <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
@@ -1870,7 +1870,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1900,7 +1900,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1985,7 +1985,7 @@
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2256,13 +2256,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>18.7</v>
@@ -2292,7 +2292,7 @@
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2359,7 +2359,7 @@
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
@@ -2377,10 +2377,10 @@
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
@@ -2447,10 +2447,10 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>22.1</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
@@ -2459,7 +2459,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2529,10 +2529,10 @@
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.4</v>
@@ -2617,7 +2617,7 @@
         <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.9</v>
@@ -2656,10 +2656,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2702,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7.1</v>
@@ -2772,13 +2772,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.1</v>
@@ -2863,7 +2863,7 @@
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2902,7 +2902,7 @@
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>27.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>131.2</v>
@@ -2951,7 +2951,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -2987,7 +2987,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.8</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>55.4</v>
@@ -3024,10 +3024,10 @@
         <v>457</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>18.3</v>
@@ -3052,7 +3052,7 @@
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3088,7 +3088,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>25.8</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>21.1</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
@@ -3218,7 +3218,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3285,7 +3285,7 @@
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.5</v>
@@ -3303,7 +3303,7 @@
         <v>15.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3336,7 +3336,7 @@
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3406,7 +3406,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3479,7 +3479,7 @@
         <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3494,7 +3494,7 @@
         <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>224.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>128.5</v>
@@ -3540,7 +3540,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>14.1</v>
@@ -3561,20 +3561,20 @@
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="3" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>16.4</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3586,7 +3586,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3629,7 +3629,7 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.1</v>
+        <v>22.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3662,7 +3662,7 @@
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
@@ -3696,7 +3696,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>26.9</v>
+        <v>269.2</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>11</v>
@@ -3708,7 +3708,7 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.5</v>
@@ -3726,7 +3726,7 @@
         <v>12.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3809,13 +3809,13 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>22</v>
@@ -3876,7 +3876,7 @@
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
@@ -3930,7 +3930,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -3988,7 +3988,7 @@
         <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>2.6</v>
+        <v>26.6</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>17.6</v>
@@ -3997,7 +3997,7 @@
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.3</v>
+        <v>23.2</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
@@ -4113,10 +4113,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4134,13 +4134,13 @@
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4207,10 +4207,10 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.2</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>111100</v>
+        <v>101.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>11.8</v>
@@ -4249,7 +4249,7 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>65.7</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -763,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.1</v>
@@ -881,7 +872,7 @@
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -890,7 +881,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -960,7 +951,7 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
@@ -1012,7 +1003,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1024,7 +1015,7 @@
         <v>13.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
@@ -1094,7 +1085,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1161,7 +1152,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.9</v>
+        <v>17.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
@@ -1207,7 +1198,7 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1287,7 +1278,7 @@
         <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>27.1</v>
+        <v>17.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
@@ -1325,7 +1316,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>504.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>27.3</v>
@@ -1355,7 +1346,7 @@
         <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1373,7 +1364,7 @@
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>26.8</v>
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>42</v>
@@ -1464,13 +1455,13 @@
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
@@ -1513,7 +1504,7 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
@@ -1525,7 +1516,7 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>18.6</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>13.6</v>
@@ -1546,7 +1537,7 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1601,13 +1592,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1634,7 +1625,7 @@
         <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>14.5</v>
@@ -1754,7 +1745,7 @@
         <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>568.8</v>
+        <v>568.1</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92.5</v>
@@ -1870,7 +1861,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1885,7 +1876,7 @@
         <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>19.6</v>
@@ -1900,7 +1891,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,7 +1925,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1985,7 +1976,7 @@
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2125,7 +2116,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
@@ -2171,7 +2162,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>382.4</v>
+        <v>38.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>24.8</v>
@@ -2192,7 +2183,7 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2256,7 +2247,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
+        <v>309</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
@@ -2292,7 +2283,7 @@
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2341,7 +2332,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
+        <v>232</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>132.1</v>
@@ -2380,7 +2371,7 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
@@ -2450,7 +2441,7 @@
         <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
@@ -2459,7 +2450,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2535,7 +2526,7 @@
         <v>4.1</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>10.1</v>
@@ -2547,7 +2538,7 @@
         <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.4</v>
@@ -2656,10 +2647,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>142.2</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2747,7 +2738,7 @@
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2863,7 +2854,7 @@
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2902,7 +2893,7 @@
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2936,7 +2927,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
+        <v>228.4</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>131.2</v>
@@ -2951,7 +2942,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3027,7 +3018,7 @@
         <v>26.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>18.3</v>
@@ -3052,7 +3043,7 @@
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3088,7 +3079,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3137,7 +3128,7 @@
         <v>10.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>97</v>
@@ -3155,7 +3146,7 @@
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="n">
@@ -3218,7 +3209,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3336,7 +3327,7 @@
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3406,7 +3397,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3479,7 +3470,7 @@
         <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3491,7 +3482,7 @@
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>17.9</v>
@@ -3586,7 +3577,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82.7</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3626,7 +3617,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>22.1</v>
@@ -3696,7 +3687,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>269.2</v>
+        <v>26.9</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>11</v>
@@ -3915,7 +3906,7 @@
         <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>22</v>
@@ -3930,7 +3921,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3997,7 +3988,7 @@
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
@@ -4023,7 +4014,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
@@ -4062,7 +4053,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
@@ -4101,7 +4092,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
+        <v>191.1</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>109.7</v>
@@ -4116,7 +4107,7 @@
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4140,7 +4131,7 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4164,7 +4155,7 @@
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4207,10 +4198,10 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>101.1</v>
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>11.8</v>
@@ -4252,7 +4243,7 @@
         <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>65.7</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>8.9</v>
